--- a/artfynd/A 62142-2025 artfynd.xlsx
+++ b/artfynd/A 62142-2025 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>137517040</v>
       </c>
       <c r="B3" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>137517023</v>
       </c>
       <c r="B4" t="n">
-        <v>99437</v>
+        <v>99440</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>137517042</v>
       </c>
       <c r="B5" t="n">
-        <v>102793</v>
+        <v>102796</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
